--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_vsync_svsync.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_vsync_svsync.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824873E7-F852-4251-99BC-BD0A4A579E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71197596-EE03-4C18-A50F-AE8508CEB4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:CG25"/>
+  <dimension ref="B3:CG27"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
@@ -796,73 +796,73 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B19">
-        <f>$B$10/C18</f>
-        <v>7680</v>
-      </c>
-      <c r="C19" t="s">
-        <v>2</v>
+      <c r="C19" s="4">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B20">
-        <f>1000/B19</f>
-        <v>0.13020833333333334</v>
+        <f>$B$10/C19</f>
+        <v>19200</v>
       </c>
       <c r="C20" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B21">
-        <f>90000000/B19</f>
-        <v>11718.75</v>
+        <f>1000/B20</f>
+        <v>5.2083333333333336E-2</v>
       </c>
       <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <f>90000000/B20</f>
+        <v>4687.5</v>
+      </c>
+      <c r="C22" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B23">
-        <f>$B$10/C22</f>
-        <v>7680</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B24">
-        <f>1000/B23</f>
-        <v>0.13020833333333334</v>
-      </c>
-      <c r="C24" t="s">
-        <v>5</v>
+      <c r="C24" s="4">
+        <v>0.8</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B25">
-        <f>90000000/B23</f>
-        <v>11718.75</v>
+        <f>$B$10/C24</f>
+        <v>4800</v>
       </c>
       <c r="C25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <f>1000/B25</f>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B27">
+        <f>90000000/B25</f>
+        <v>18750</v>
+      </c>
+      <c r="C27" t="s">
         <v>8</v>
       </c>
     </row>

--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_vsync_svsync.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_vsync_svsync.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71197596-EE03-4C18-A50F-AE8508CEB4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67BA6BF-81D7-4CE2-B834-917BC2F9F1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="86295" yWindow="2280" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -801,13 +801,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="4">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B20">
         <f>$B$10/C19</f>
-        <v>19200</v>
+        <v>7680</v>
       </c>
       <c r="C20" t="s">
         <v>2</v>
@@ -816,7 +816,7 @@
     <row r="21" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B21">
         <f>1000/B20</f>
-        <v>5.2083333333333336E-2</v>
+        <v>0.13020833333333334</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -825,7 +825,7 @@
     <row r="22" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B22">
         <f>90000000/B20</f>
-        <v>4687.5</v>
+        <v>11718.75</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
@@ -836,13 +836,13 @@
         <v>7</v>
       </c>
       <c r="C24" s="4">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B25">
         <f>$B$10/C24</f>
-        <v>4800</v>
+        <v>7680</v>
       </c>
       <c r="C25" t="s">
         <v>2</v>
@@ -851,7 +851,7 @@
     <row r="26" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B26">
         <f>1000/B25</f>
-        <v>0.20833333333333334</v>
+        <v>0.13020833333333334</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -860,7 +860,7 @@
     <row r="27" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B27">
         <f>90000000/B25</f>
-        <v>18750</v>
+        <v>11718.75</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>

--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_vsync_svsync.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_vsync_svsync.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67BA6BF-81D7-4CE2-B834-917BC2F9F1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017FDAA5-6283-4C59-AD0B-A4BCB5F63902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="86295" yWindow="2280" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
   <si>
     <t>Main Vsync</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,10 +79,6 @@
   </si>
   <si>
     <t>90MHz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -159,13 +155,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -765,14 +760,12 @@
       <c r="B14" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="C14" s="4"/>
     </row>
     <row r="15" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B15" t="e">
         <f>$B$10/C14</f>
-        <v>#VALUE!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="C15" t="s">
         <v>2</v>
@@ -781,7 +774,7 @@
     <row r="16" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B16" t="e">
         <f>1000/B15</f>
-        <v>#VALUE!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -790,7 +783,7 @@
     <row r="17" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B17" t="e">
         <f>90000000/B15</f>
-        <v>#VALUE!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>

--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_vsync_svsync.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_vsync_svsync.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017FDAA5-6283-4C59-AD0B-A4BCB5F63902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB6490F-DCDB-41DB-A029-677A6E5D3E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="RGB" sheetId="1" r:id="rId1"/>
+    <sheet name="R+GB" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="11">
   <si>
     <t>Main Vsync</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -102,12 +103,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -155,12 +162,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -441,12 +449,567 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B3:BY27"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="77" width="3.9140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="3"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1"/>
+      <c r="BC3" s="1"/>
+      <c r="BD3" s="1"/>
+      <c r="BE3" s="1"/>
+      <c r="BF3" s="1"/>
+      <c r="BG3" s="1"/>
+      <c r="BH3" s="1"/>
+      <c r="BI3" s="1"/>
+      <c r="BJ3" s="1"/>
+      <c r="BK3" s="1"/>
+      <c r="BL3" s="1"/>
+      <c r="BM3" s="1"/>
+      <c r="BN3" s="1"/>
+      <c r="BO3" s="1"/>
+      <c r="BP3" s="1"/>
+      <c r="BQ3" s="1"/>
+      <c r="BR3" s="1"/>
+      <c r="BS3" s="1"/>
+      <c r="BT3" s="1"/>
+      <c r="BU3" s="1"/>
+      <c r="BV3" s="1"/>
+      <c r="BW3" s="1"/>
+      <c r="BX3" s="1"/>
+      <c r="BY3" s="1"/>
+    </row>
+    <row r="4" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B4">
+        <v>120</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B5">
+        <f>1000/B4</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B9" s="4">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="1"/>
+      <c r="AO9" s="1"/>
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="3"/>
+      <c r="AR9" s="1"/>
+      <c r="AS9" s="1"/>
+      <c r="AT9" s="1"/>
+      <c r="AU9" s="1"/>
+      <c r="AV9" s="1"/>
+      <c r="AW9" s="1"/>
+      <c r="AX9" s="1"/>
+      <c r="AY9" s="2"/>
+      <c r="AZ9" s="3"/>
+      <c r="BA9" s="1"/>
+      <c r="BB9" s="1"/>
+      <c r="BC9" s="1"/>
+      <c r="BD9" s="1"/>
+      <c r="BE9" s="1"/>
+      <c r="BF9" s="1"/>
+      <c r="BG9" s="1"/>
+      <c r="BH9" s="2"/>
+      <c r="BI9" s="3"/>
+      <c r="BJ9" s="1"/>
+      <c r="BK9" s="1"/>
+      <c r="BL9" s="1"/>
+      <c r="BM9" s="1"/>
+      <c r="BN9" s="1"/>
+      <c r="BO9" s="1"/>
+      <c r="BP9" s="1"/>
+      <c r="BQ9" s="2"/>
+      <c r="BR9" s="3"/>
+      <c r="BS9" s="1"/>
+      <c r="BT9" s="1"/>
+      <c r="BU9" s="1"/>
+      <c r="BV9" s="1"/>
+      <c r="BW9" s="1"/>
+      <c r="BX9" s="1"/>
+      <c r="BY9" s="1"/>
+    </row>
+    <row r="10" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B10">
+        <f>B4*B9</f>
+        <v>3840</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B11">
+        <f>1000/B10</f>
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="5">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="2"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="1"/>
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+      <c r="AO14" s="1"/>
+      <c r="AP14" s="2"/>
+      <c r="AQ14" s="3"/>
+      <c r="AR14" s="1"/>
+      <c r="AS14" s="1"/>
+      <c r="AT14" s="1"/>
+      <c r="AU14" s="1"/>
+      <c r="AV14" s="1"/>
+      <c r="AW14" s="1"/>
+      <c r="AX14" s="1"/>
+      <c r="AY14" s="2"/>
+      <c r="AZ14" s="3"/>
+      <c r="BA14" s="1"/>
+      <c r="BB14" s="1"/>
+      <c r="BC14" s="1"/>
+      <c r="BD14" s="1"/>
+      <c r="BE14" s="1"/>
+      <c r="BF14" s="1"/>
+      <c r="BG14" s="1"/>
+      <c r="BH14" s="2"/>
+      <c r="BI14" s="3"/>
+      <c r="BJ14" s="1"/>
+      <c r="BK14" s="1"/>
+      <c r="BL14" s="1"/>
+      <c r="BM14" s="1"/>
+      <c r="BN14" s="1"/>
+      <c r="BO14" s="1"/>
+      <c r="BP14" s="1"/>
+      <c r="BQ14" s="2"/>
+      <c r="BR14" s="3"/>
+      <c r="BS14" s="1"/>
+      <c r="BT14" s="1"/>
+      <c r="BU14" s="1"/>
+      <c r="BV14" s="1"/>
+      <c r="BW14" s="1"/>
+      <c r="BX14" s="1"/>
+      <c r="BY14" s="1"/>
+    </row>
+    <row r="15" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B15">
+        <f>$B$10/C14</f>
+        <v>11520</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <f>1000/B15</f>
+        <v>8.6805555555555552E-2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <f>90000000/B15</f>
+        <v>7812.5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="1"/>
+      <c r="AO19" s="1"/>
+      <c r="AP19" s="1"/>
+      <c r="AQ19" s="1"/>
+      <c r="AR19" s="1"/>
+      <c r="AS19" s="2"/>
+      <c r="AT19" s="3"/>
+      <c r="AU19" s="1"/>
+      <c r="AV19" s="1"/>
+      <c r="AW19" s="1"/>
+      <c r="AX19" s="1"/>
+      <c r="AY19" s="1"/>
+      <c r="AZ19" s="1"/>
+      <c r="BA19" s="1"/>
+      <c r="BB19" s="2"/>
+      <c r="BC19" s="3"/>
+      <c r="BD19" s="1"/>
+      <c r="BE19" s="1"/>
+      <c r="BF19" s="1"/>
+      <c r="BG19" s="1"/>
+      <c r="BH19" s="1"/>
+      <c r="BI19" s="1"/>
+      <c r="BJ19" s="1"/>
+      <c r="BK19" s="2"/>
+      <c r="BL19" s="3"/>
+      <c r="BM19" s="1"/>
+      <c r="BN19" s="1"/>
+      <c r="BO19" s="1"/>
+      <c r="BP19" s="1"/>
+      <c r="BQ19" s="1"/>
+      <c r="BR19" s="1"/>
+      <c r="BS19" s="1"/>
+      <c r="BT19" s="2"/>
+      <c r="BU19" s="3"/>
+      <c r="BV19" s="1"/>
+      <c r="BW19" s="1"/>
+      <c r="BX19" s="1"/>
+      <c r="BY19" s="1"/>
+    </row>
+    <row r="20" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B20">
+        <f>$B$10/C19</f>
+        <v>11520</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B21">
+        <f>1000/B20</f>
+        <v>8.6805555555555552E-2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <f>90000000/B20</f>
+        <v>7812.5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="5">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="1"/>
+      <c r="AM24" s="2"/>
+      <c r="AN24" s="3"/>
+      <c r="AO24" s="1"/>
+      <c r="AP24" s="1"/>
+      <c r="AQ24" s="1"/>
+      <c r="AR24" s="1"/>
+      <c r="AS24" s="1"/>
+      <c r="AT24" s="1"/>
+      <c r="AU24" s="1"/>
+      <c r="AV24" s="2"/>
+      <c r="AW24" s="3"/>
+      <c r="AX24" s="1"/>
+      <c r="AY24" s="1"/>
+      <c r="AZ24" s="1"/>
+      <c r="BA24" s="1"/>
+      <c r="BB24" s="1"/>
+      <c r="BC24" s="1"/>
+      <c r="BD24" s="1"/>
+      <c r="BE24" s="2"/>
+      <c r="BF24" s="3"/>
+      <c r="BG24" s="1"/>
+      <c r="BH24" s="1"/>
+      <c r="BI24" s="1"/>
+      <c r="BJ24" s="1"/>
+      <c r="BK24" s="1"/>
+      <c r="BL24" s="1"/>
+      <c r="BM24" s="1"/>
+      <c r="BN24" s="2"/>
+      <c r="BO24" s="3"/>
+      <c r="BP24" s="1"/>
+      <c r="BQ24" s="1"/>
+      <c r="BR24" s="1"/>
+      <c r="BS24" s="1"/>
+      <c r="BT24" s="1"/>
+      <c r="BU24" s="1"/>
+      <c r="BV24" s="1"/>
+      <c r="BW24" s="2"/>
+      <c r="BX24" s="3"/>
+      <c r="BY24" s="1"/>
+    </row>
+    <row r="25" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B25">
+        <f>$B$10/C24</f>
+        <v>11520</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <f>1000/B25</f>
+        <v>8.6805555555555552E-2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:77" x14ac:dyDescent="0.45">
+      <c r="B27">
+        <f>90000000/B25</f>
+        <v>7812.5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F568020-6746-44B9-BB2A-24C50CF1C4F3}">
   <dimension ref="B3:CG27"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="104" width="3.9140625" customWidth="1"/>
+    <col min="4" max="85" width="3.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:85" x14ac:dyDescent="0.45">
@@ -562,7 +1125,7 @@
       </c>
     </row>
     <row r="9" spans="2:85" x14ac:dyDescent="0.45">
-      <c r="B9">
+      <c r="B9" s="4">
         <v>32</v>
       </c>
       <c r="C9" t="s">
@@ -673,94 +1236,94 @@
       <c r="C13" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="1"/>
-      <c r="AC13" s="1"/>
-      <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="2"/>
-      <c r="AG13" s="1"/>
-      <c r="AH13" s="1"/>
-      <c r="AI13" s="2"/>
-      <c r="AJ13" s="2"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="1"/>
-      <c r="AM13" s="1"/>
-      <c r="AN13" s="1"/>
-      <c r="AO13" s="1"/>
-      <c r="AP13" s="2"/>
-      <c r="AQ13" s="1"/>
-      <c r="AR13" s="1"/>
-      <c r="AS13" s="2"/>
-      <c r="AT13" s="2"/>
-      <c r="AU13" s="3"/>
-      <c r="AV13" s="1"/>
-      <c r="AW13" s="1"/>
-      <c r="AX13" s="1"/>
-      <c r="AY13" s="1"/>
-      <c r="AZ13" s="2"/>
-      <c r="BA13" s="1"/>
-      <c r="BB13" s="1"/>
-      <c r="BC13" s="2"/>
-      <c r="BD13" s="2"/>
-      <c r="BE13" s="3"/>
-      <c r="BF13" s="1"/>
-      <c r="BG13" s="1"/>
-      <c r="BH13" s="1"/>
-      <c r="BI13" s="1"/>
-      <c r="BJ13" s="2"/>
-      <c r="BK13" s="1"/>
-      <c r="BL13" s="1"/>
-      <c r="BM13" s="2"/>
-      <c r="BN13" s="2"/>
-      <c r="BO13" s="3"/>
-      <c r="BP13" s="1"/>
-      <c r="BQ13" s="1"/>
-      <c r="BR13" s="1"/>
-      <c r="BS13" s="1"/>
-      <c r="BT13" s="2"/>
-      <c r="BU13" s="1"/>
-      <c r="BV13" s="1"/>
-      <c r="BW13" s="2"/>
-      <c r="BX13" s="2"/>
-      <c r="BY13" s="3"/>
-      <c r="BZ13" s="1"/>
-      <c r="CA13" s="1"/>
-      <c r="CB13" s="1"/>
-      <c r="CC13" s="1"/>
-      <c r="CD13" s="2"/>
-      <c r="CE13" s="1"/>
-      <c r="CF13" s="1"/>
-      <c r="CG13" s="2"/>
     </row>
     <row r="14" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="1"/>
+      <c r="AI14" s="1"/>
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+      <c r="AO14" s="1"/>
+      <c r="AP14" s="1"/>
+      <c r="AQ14" s="1"/>
+      <c r="AR14" s="1"/>
+      <c r="AS14" s="1"/>
+      <c r="AT14" s="2"/>
+      <c r="AU14" s="3"/>
+      <c r="AV14" s="1"/>
+      <c r="AW14" s="1"/>
+      <c r="AX14" s="1"/>
+      <c r="AY14" s="1"/>
+      <c r="AZ14" s="1"/>
+      <c r="BA14" s="1"/>
+      <c r="BB14" s="1"/>
+      <c r="BC14" s="1"/>
+      <c r="BD14" s="1"/>
+      <c r="BE14" s="1"/>
+      <c r="BF14" s="1"/>
+      <c r="BG14" s="1"/>
+      <c r="BH14" s="1"/>
+      <c r="BI14" s="1"/>
+      <c r="BJ14" s="1"/>
+      <c r="BK14" s="1"/>
+      <c r="BL14" s="1"/>
+      <c r="BM14" s="1"/>
+      <c r="BN14" s="1"/>
+      <c r="BO14" s="1"/>
+      <c r="BP14" s="1"/>
+      <c r="BQ14" s="1"/>
+      <c r="BR14" s="1"/>
+      <c r="BS14" s="1"/>
+      <c r="BT14" s="1"/>
+      <c r="BU14" s="1"/>
+      <c r="BV14" s="1"/>
+      <c r="BW14" s="1"/>
+      <c r="BX14" s="1"/>
+      <c r="BY14" s="1"/>
+      <c r="BZ14" s="1"/>
+      <c r="CA14" s="1"/>
+      <c r="CB14" s="1"/>
+      <c r="CC14" s="1"/>
+      <c r="CD14" s="1"/>
+      <c r="CE14" s="1"/>
+      <c r="CF14" s="1"/>
+      <c r="CG14" s="1"/>
     </row>
     <row r="15" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B15" t="e">
@@ -780,7 +1343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B17" t="e">
         <f>90000000/B15</f>
         <v>#DIV/0!</v>
@@ -789,15 +1352,98 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
+        <f>1/2</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="1"/>
+      <c r="AO19" s="1"/>
+      <c r="AP19" s="1"/>
+      <c r="AQ19" s="1"/>
+      <c r="AR19" s="1"/>
+      <c r="AS19" s="1"/>
+      <c r="AT19" s="2"/>
+      <c r="AU19" s="3"/>
+      <c r="AV19" s="1"/>
+      <c r="AW19" s="1"/>
+      <c r="AX19" s="1"/>
+      <c r="AY19" s="1"/>
+      <c r="AZ19" s="1"/>
+      <c r="BA19" s="1"/>
+      <c r="BB19" s="1"/>
+      <c r="BC19" s="1"/>
+      <c r="BD19" s="2"/>
+      <c r="BE19" s="3"/>
+      <c r="BF19" s="1"/>
+      <c r="BG19" s="1"/>
+      <c r="BH19" s="1"/>
+      <c r="BI19" s="1"/>
+      <c r="BJ19" s="1"/>
+      <c r="BK19" s="1"/>
+      <c r="BL19" s="1"/>
+      <c r="BM19" s="1"/>
+      <c r="BN19" s="2"/>
+      <c r="BO19" s="3"/>
+      <c r="BP19" s="1"/>
+      <c r="BQ19" s="1"/>
+      <c r="BR19" s="1"/>
+      <c r="BS19" s="1"/>
+      <c r="BT19" s="1"/>
+      <c r="BU19" s="1"/>
+      <c r="BV19" s="1"/>
+      <c r="BW19" s="1"/>
+      <c r="BX19" s="2"/>
+      <c r="BY19" s="3"/>
+      <c r="BZ19" s="1"/>
+      <c r="CA19" s="1"/>
+      <c r="CB19" s="1"/>
+      <c r="CC19" s="1"/>
+      <c r="CD19" s="1"/>
+      <c r="CE19" s="1"/>
+      <c r="CF19" s="1"/>
+      <c r="CG19" s="1"/>
+    </row>
+    <row r="20" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B20">
         <f>$B$10/C19</f>
         <v>7680</v>
@@ -806,7 +1452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B21">
         <f>1000/B20</f>
         <v>0.13020833333333334</v>
@@ -815,7 +1461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B22">
         <f>90000000/B20</f>
         <v>11718.75</v>
@@ -824,15 +1470,98 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
+        <f>1/2</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="1"/>
+      <c r="AM24" s="1"/>
+      <c r="AN24" s="1"/>
+      <c r="AO24" s="2"/>
+      <c r="AP24" s="3"/>
+      <c r="AQ24" s="1"/>
+      <c r="AR24" s="1"/>
+      <c r="AS24" s="1"/>
+      <c r="AT24" s="1"/>
+      <c r="AU24" s="1"/>
+      <c r="AV24" s="1"/>
+      <c r="AW24" s="1"/>
+      <c r="AX24" s="1"/>
+      <c r="AY24" s="2"/>
+      <c r="AZ24" s="3"/>
+      <c r="BA24" s="1"/>
+      <c r="BB24" s="1"/>
+      <c r="BC24" s="1"/>
+      <c r="BD24" s="1"/>
+      <c r="BE24" s="1"/>
+      <c r="BF24" s="1"/>
+      <c r="BG24" s="1"/>
+      <c r="BH24" s="1"/>
+      <c r="BI24" s="2"/>
+      <c r="BJ24" s="3"/>
+      <c r="BK24" s="1"/>
+      <c r="BL24" s="1"/>
+      <c r="BM24" s="1"/>
+      <c r="BN24" s="1"/>
+      <c r="BO24" s="1"/>
+      <c r="BP24" s="1"/>
+      <c r="BQ24" s="1"/>
+      <c r="BR24" s="1"/>
+      <c r="BS24" s="2"/>
+      <c r="BT24" s="3"/>
+      <c r="BU24" s="1"/>
+      <c r="BV24" s="1"/>
+      <c r="BW24" s="1"/>
+      <c r="BX24" s="1"/>
+      <c r="BY24" s="1"/>
+      <c r="BZ24" s="1"/>
+      <c r="CA24" s="1"/>
+      <c r="CB24" s="1"/>
+      <c r="CC24" s="2"/>
+      <c r="CD24" s="3"/>
+      <c r="CE24" s="1"/>
+      <c r="CF24" s="1"/>
+      <c r="CG24" s="1"/>
+    </row>
+    <row r="25" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B25">
         <f>$B$10/C24</f>
         <v>7680</v>
@@ -841,7 +1570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B26">
         <f>1000/B25</f>
         <v>0.13020833333333334</v>
@@ -850,7 +1579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:85" x14ac:dyDescent="0.45">
       <c r="B27">
         <f>90000000/B25</f>
         <v>11718.75</v>
